--- a/data/trans_dic/P20-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P20-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,74</t>
+          <t>0,9; 3,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,34</t>
+          <t>1,95; 5,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,07</t>
+          <t>1,62; 4,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,76</t>
+          <t>4,01; 8,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 11,18</t>
+          <t>5,71; 11,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 11,73</t>
+          <t>6,12; 11,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 12,71</t>
+          <t>3,96; 12,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,49</t>
+          <t>2,82; 5,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,54</t>
+          <t>4,29; 7,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,72</t>
+          <t>4,23; 7,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,73</t>
+          <t>1,73; 5,81</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,67</t>
+          <t>2,03; 4,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,37</t>
+          <t>3,04; 6,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,88</t>
+          <t>1,2; 4,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,84</t>
+          <t>1,67; 7,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 14,84</t>
+          <t>9,4; 14,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 17,28</t>
+          <t>11,47; 17,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 13,94</t>
+          <t>8,39; 13,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,29</t>
+          <t>4,42; 10,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 8,65</t>
+          <t>5,87; 8,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,88</t>
+          <t>7,5; 10,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,11</t>
+          <t>5,05; 7,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,77</t>
+          <t>3,93; 7,67</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,54</t>
+          <t>1,76; 4,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,82</t>
+          <t>3,85; 7,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,24</t>
+          <t>2,19; 5,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,07</t>
+          <t>2,39; 6,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,94</t>
+          <t>3,32; 6,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,38</t>
+          <t>6,11; 10,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 10,11</t>
+          <t>5,95; 10,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,73</t>
+          <t>5,0; 8,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,0</t>
+          <t>3,03; 5,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,21</t>
+          <t>5,34; 8,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,04</t>
+          <t>4,34; 7,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,52</t>
+          <t>4,14; 6,69</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,64</t>
+          <t>2,76; 6,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,47</t>
+          <t>3,66; 7,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,18</t>
+          <t>2,27; 5,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,57</t>
+          <t>1,59; 6,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,25</t>
+          <t>3,38; 7,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,87</t>
+          <t>5,99; 10,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,86</t>
+          <t>3,33; 7,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,45</t>
+          <t>3,05; 5,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,12</t>
+          <t>3,41; 6,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,42</t>
+          <t>5,42; 8,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,46</t>
+          <t>3,09; 5,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,39</t>
+          <t>2,48; 5,48</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,51</t>
+          <t>3,42; 7,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,23</t>
+          <t>4,37; 8,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,99</t>
+          <t>5,0; 9,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 10,58</t>
+          <t>6,24; 10,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,91</t>
+          <t>3,81; 8,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,47</t>
+          <t>4,8; 9,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,39</t>
+          <t>3,32; 7,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,83</t>
+          <t>4,04; 7,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,37</t>
+          <t>4,1; 7,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,61</t>
+          <t>5,12; 8,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,77</t>
+          <t>4,44; 7,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,28</t>
+          <t>5,59; 8,32</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,05; 11,32</t>
+          <t>5,37; 11,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 14,0</t>
+          <t>6,34; 13,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 14,88</t>
+          <t>7,76; 15,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 12,0</t>
+          <t>7,46; 12,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,8</t>
+          <t>5,91; 11,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,73</t>
+          <t>6,89; 13,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,49</t>
+          <t>5,23; 10,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,08</t>
+          <t>1,51; 6,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,74</t>
+          <t>6,22; 10,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,99</t>
+          <t>7,38; 12,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,48</t>
+          <t>7,16; 11,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,96</t>
+          <t>2,92; 7,98</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 13,82</t>
+          <t>5,87; 14,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,25</t>
+          <t>10,17; 19,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,55; 12,05</t>
+          <t>5,75; 12,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 14,0</t>
+          <t>8,35; 14,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 13,95</t>
+          <t>6,79; 13,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,57; 15,29</t>
+          <t>8,22; 14,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 14,35</t>
+          <t>6,93; 13,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,94</t>
+          <t>7,62; 11,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 12,38</t>
+          <t>7,21; 12,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,22; 15,59</t>
+          <t>10,15; 15,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,06; 12,17</t>
+          <t>7,25; 11,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,4; 11,92</t>
+          <t>8,55; 12,11</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,92</t>
+          <t>3,49; 4,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,02</t>
+          <t>5,24; 6,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,6</t>
+          <t>4,09; 5,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,34</t>
+          <t>4,25; 6,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,44</t>
+          <t>6,55; 8,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,54; 10,53</t>
+          <t>8,58; 10,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,65</t>
+          <t>6,84; 8,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,82</t>
+          <t>4,81; 6,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,34</t>
+          <t>5,23; 6,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,18; 8,48</t>
+          <t>7,14; 8,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,89</t>
+          <t>5,72; 6,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,9; 6,32</t>
+          <t>4,86; 6,3</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4844; 18441</t>
+          <t>4435; 17974</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8673; 24157</t>
+          <t>8816; 24848</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6431; 21254</t>
+          <t>6779; 20676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7592</t>
+          <t>0; 7547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19777; 40955</t>
+          <t>18758; 40200</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24499; 48119</t>
+          <t>24562; 48205</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23915; 46404</t>
+          <t>24218; 47128</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12301; 39813</t>
+          <t>12390; 38631</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27162; 52775</t>
+          <t>27129; 51998</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37355; 66544</t>
+          <t>37878; 64751</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35091; 62899</t>
+          <t>34471; 61877</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12336; 40842</t>
+          <t>12367; 41404</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14905; 34366</t>
+          <t>14913; 34480</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21557; 43762</t>
+          <t>20870; 44074</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6969; 22895</t>
+          <t>7085; 23787</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6494; 28983</t>
+          <t>7058; 29853</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59693; 92829</t>
+          <t>58818; 92415</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71611; 105450</t>
+          <t>70021; 105311</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48044; 78544</t>
+          <t>47266; 76949</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22429; 52650</t>
+          <t>22627; 52564</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80176; 117679</t>
+          <t>79887; 118601</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97203; 141145</t>
+          <t>97311; 139380</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60111; 93595</t>
+          <t>58331; 91569</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37368; 72625</t>
+          <t>36719; 71683</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11418; 28970</t>
+          <t>11259; 27187</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26148; 53336</t>
+          <t>26242; 53627</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14124; 35045</t>
+          <t>14684; 35360</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12281; 32579</t>
+          <t>12843; 32357</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24646; 47896</t>
+          <t>22876; 46199</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44150; 73778</t>
+          <t>43451; 73539</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38099; 66855</t>
+          <t>39337; 66768</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27170; 47380</t>
+          <t>27106; 46114</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39058; 66399</t>
+          <t>40186; 67064</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75032; 114278</t>
+          <t>74411; 114819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59280; 93631</t>
+          <t>57794; 94406</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44187; 70345</t>
+          <t>44689; 72215</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14082; 34446</t>
+          <t>14333; 34848</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23068; 45920</t>
+          <t>22506; 45188</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14079; 33442</t>
+          <t>14668; 33603</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15421; 58344</t>
+          <t>14146; 58009</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17875; 37392</t>
+          <t>17412; 37291</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36728; 66995</t>
+          <t>36922; 67595</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22097; 44542</t>
+          <t>21607; 46521</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21285; 38833</t>
+          <t>21742; 38025</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35653; 63311</t>
+          <t>35285; 64274</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66784; 103617</t>
+          <t>66686; 102694</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40829; 70670</t>
+          <t>40064; 69613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40854; 86203</t>
+          <t>39680; 87761</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12445; 29029</t>
+          <t>13225; 28870</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18884; 39624</t>
+          <t>18750; 38509</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23482; 47748</t>
+          <t>23891; 47616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34340; 59368</t>
+          <t>35028; 58971</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16324; 35975</t>
+          <t>15390; 35704</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20638; 42407</t>
+          <t>21475; 42995</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17243; 36693</t>
+          <t>16487; 37151</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21978; 37255</t>
+          <t>22020; 38260</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32775; 58309</t>
+          <t>32421; 57156</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44871; 75494</t>
+          <t>44885; 74250</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46188; 75710</t>
+          <t>43298; 76634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>62404; 91683</t>
+          <t>61900; 92105</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14765; 33112</t>
+          <t>15714; 33522</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20211; 43372</t>
+          <t>19637; 40931</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25887; 49759</t>
+          <t>25930; 50233</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26461; 44188</t>
+          <t>27476; 46076</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21312; 40455</t>
+          <t>20252; 39871</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23794; 45078</t>
+          <t>24402; 46060</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19955; 43399</t>
+          <t>19753; 41027</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7741; 36991</t>
+          <t>9209; 37569</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40019; 68228</t>
+          <t>39558; 65549</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48366; 79604</t>
+          <t>48988; 80141</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50756; 81732</t>
+          <t>51011; 83281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28889; 77774</t>
+          <t>28518; 77922</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12344; 29016</t>
+          <t>12310; 29552</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25526; 50605</t>
+          <t>25416; 49815</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14251; 30976</t>
+          <t>14775; 31512</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23238; 39596</t>
+          <t>23611; 39806</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23272; 46579</t>
+          <t>22673; 46064</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33319; 59490</t>
+          <t>31992; 57681</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28402; 57416</t>
+          <t>27725; 54933</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>32776; 50861</t>
+          <t>32440; 49797</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>39286; 67313</t>
+          <t>39215; 67110</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65286; 99604</t>
+          <t>64873; 100318</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46416; 79963</t>
+          <t>47631; 78647</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>59515; 84479</t>
+          <t>60563; 85840</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>114463; 161027</t>
+          <t>114249; 160390</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>181142; 240563</t>
+          <t>179576; 238955</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>138465; 190218</t>
+          <t>138742; 189650</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>148604; 219461</t>
+          <t>147065; 219115</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>221883; 285315</t>
+          <t>221283; 281499</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>304031; 374818</t>
+          <t>305250; 377915</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>241903; 306475</t>
+          <t>242355; 309016</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>177874; 249496</t>
+          <t>175872; 249986</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>350217; 422044</t>
+          <t>347926; 424115</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>501689; 591963</t>
+          <t>498597; 594004</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>396890; 477952</t>
+          <t>396945; 480834</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>348675; 450091</t>
+          <t>346082; 448675</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P20-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,64</t>
+          <t>0,99; 4,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,5</t>
+          <t>1,97; 5,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,93</t>
+          <t>1,58; 4,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,6</t>
+          <t>4,21; 8,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 11,2</t>
+          <t>5,9; 11,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 11,91</t>
+          <t>5,96; 11,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 12,33</t>
+          <t>3,76; 12,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,41</t>
+          <t>2,78; 5,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,34</t>
+          <t>4,27; 7,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,59</t>
+          <t>4,15; 7,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,81</t>
+          <t>1,92; 6,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,69</t>
+          <t>2,08; 4,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,41</t>
+          <t>3,03; 6,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,03</t>
+          <t>1,17; 3,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,05</t>
+          <t>1,61; 6,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 14,77</t>
+          <t>9,56; 14,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 17,26</t>
+          <t>11,32; 17,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 13,65</t>
+          <t>8,33; 13,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 10,28</t>
+          <t>6,19; 11,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 8,71</t>
+          <t>5,81; 8,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 10,74</t>
+          <t>7,6; 10,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 7,93</t>
+          <t>5,18; 8,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,67</t>
+          <t>4,67; 8,2</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,26</t>
+          <t>1,73; 4,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,86</t>
+          <t>3,77; 7,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,28</t>
+          <t>2,16; 5,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,03</t>
+          <t>2,39; 5,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,7</t>
+          <t>3,53; 6,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,35</t>
+          <t>6,07; 10,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,1</t>
+          <t>5,74; 10,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,5</t>
+          <t>5,03; 8,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,05</t>
+          <t>3,02; 5,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,24</t>
+          <t>5,37; 8,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,1</t>
+          <t>4,54; 7,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,69</t>
+          <t>4,15; 6,64</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,71</t>
+          <t>2,76; 6,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,35</t>
+          <t>3,66; 7,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,2</t>
+          <t>2,23; 4,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,53</t>
+          <t>4,39; 8,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,23</t>
+          <t>3,35; 7,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,97</t>
+          <t>6,25; 11,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,17</t>
+          <t>3,29; 6,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,33</t>
+          <t>3,33; 5,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,21</t>
+          <t>3,56; 6,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,34</t>
+          <t>5,46; 8,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,37</t>
+          <t>3,17; 5,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,48</t>
+          <t>4,19; 6,46</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,47</t>
+          <t>3,12; 7,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,97</t>
+          <t>4,17; 9,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,96</t>
+          <t>5,02; 9,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,51</t>
+          <t>6,29; 10,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,84</t>
+          <t>4,13; 9,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,6</t>
+          <t>4,58; 9,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,48</t>
+          <t>3,31; 7,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,01</t>
+          <t>4,17; 7,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 7,23</t>
+          <t>4,19; 7,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,46</t>
+          <t>5,21; 8,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,86</t>
+          <t>4,37; 7,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,32</t>
+          <t>5,69; 8,22</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,46</t>
+          <t>5,09; 11,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 13,21</t>
+          <t>6,43; 13,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 15,02</t>
+          <t>7,75; 15,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,51</t>
+          <t>7,11; 12,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,91; 11,63</t>
+          <t>5,93; 11,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,01</t>
+          <t>6,85; 12,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 10,86</t>
+          <t>5,23; 11,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,18</t>
+          <t>4,38; 7,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,31</t>
+          <t>6,44; 10,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 12,07</t>
+          <t>7,48; 12,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,7</t>
+          <t>7,13; 11,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,98</t>
+          <t>6,14; 8,99</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 14,08</t>
+          <t>5,73; 13,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,17; 19,94</t>
+          <t>10,19; 20,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,26</t>
+          <t>5,57; 12,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,35; 14,08</t>
+          <t>7,99; 13,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 13,8</t>
+          <t>6,84; 13,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 14,83</t>
+          <t>8,54; 15,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 13,73</t>
+          <t>6,77; 13,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,62; 11,69</t>
+          <t>7,56; 11,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 12,34</t>
+          <t>7,28; 12,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,15; 15,7</t>
+          <t>9,74; 15,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,97</t>
+          <t>7,21; 11,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 12,11</t>
+          <t>8,41; 11,67</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,9</t>
+          <t>3,48; 4,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,98</t>
+          <t>5,34; 7,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,59</t>
+          <t>4,15; 5,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,33</t>
+          <t>5,07; 6,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,33</t>
+          <t>6,44; 8,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,62</t>
+          <t>8,56; 10,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 8,72</t>
+          <t>6,86; 8,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,83</t>
+          <t>5,86; 7,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,37</t>
+          <t>5,19; 6,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,51</t>
+          <t>7,18; 8,56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,93</t>
+          <t>5,7; 6,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,3</t>
+          <t>5,66; 6,71</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>27429</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4435; 17974</t>
+          <t>4880; 19958</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8816; 24848</t>
+          <t>8884; 23616</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6779; 20676</t>
+          <t>6643; 20414</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7547</t>
+          <t>0; 6671</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18758; 40200</t>
+          <t>19677; 41718</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24562; 48205</t>
+          <t>25400; 48380</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24218; 47128</t>
+          <t>23597; 46335</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12390; 38631</t>
+          <t>13619; 44963</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27129; 51998</t>
+          <t>26695; 52882</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37878; 64751</t>
+          <t>37705; 64764</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34471; 61877</t>
+          <t>33794; 59515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12367; 41404</t>
+          <t>14791; 47219</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>42961</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52515</t>
+          <t>59934</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14913; 34480</t>
+          <t>15327; 34732</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20870; 44074</t>
+          <t>20811; 43593</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7085; 23787</t>
+          <t>6893; 23360</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7058; 29853</t>
+          <t>7654; 32013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58818; 92415</t>
+          <t>59818; 92782</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70021; 105311</t>
+          <t>69051; 105793</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47266; 76949</t>
+          <t>46922; 76267</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22627; 52564</t>
+          <t>30996; 58980</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79887; 118601</t>
+          <t>79041; 117438</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97311; 139380</t>
+          <t>98565; 140716</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58331; 91569</t>
+          <t>59830; 92815</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36719; 71683</t>
+          <t>45628; 80203</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>64838</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11259; 27187</t>
+          <t>11031; 27373</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26242; 53627</t>
+          <t>25720; 53324</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14684; 35360</t>
+          <t>14430; 34340</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12843; 32357</t>
+          <t>14866; 36322</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22876; 46199</t>
+          <t>24330; 47384</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43451; 73539</t>
+          <t>43134; 72860</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39337; 66768</t>
+          <t>37991; 66705</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27106; 46114</t>
+          <t>31300; 52397</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40186; 67064</t>
+          <t>40082; 68046</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74411; 114819</t>
+          <t>74824; 113855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57794; 94406</t>
+          <t>60435; 95280</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44689; 72215</t>
+          <t>51630; 82508</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>32515</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>75023</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14333; 34848</t>
+          <t>14343; 34311</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22506; 45188</t>
+          <t>22500; 45679</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14668; 33603</t>
+          <t>14432; 31945</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14146; 58009</t>
+          <t>30770; 58930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17412; 37291</t>
+          <t>17281; 37258</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36922; 67595</t>
+          <t>38502; 68672</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21607; 46521</t>
+          <t>21370; 44311</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21742; 38025</t>
+          <t>24530; 41986</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35285; 64274</t>
+          <t>36826; 64793</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66686; 102694</t>
+          <t>67263; 104967</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40064; 69613</t>
+          <t>41110; 72448</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39680; 87761</t>
+          <t>60284; 92868</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>49964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75677</t>
+          <t>83180</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13225; 28870</t>
+          <t>12069; 28408</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18750; 38509</t>
+          <t>17920; 39365</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23891; 47616</t>
+          <t>23992; 47408</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35028; 58971</t>
+          <t>38348; 66180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15390; 35704</t>
+          <t>16692; 37297</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21475; 42995</t>
+          <t>20505; 41561</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16487; 37151</t>
+          <t>16432; 36833</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22020; 38260</t>
+          <t>25331; 43268</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32421; 57156</t>
+          <t>33102; 57675</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44885; 74250</t>
+          <t>45662; 72683</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43298; 76634</t>
+          <t>42599; 74283</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61900; 92105</t>
+          <t>69252; 100073</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>37849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>63479</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15714; 33522</t>
+          <t>14898; 33543</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19637; 40931</t>
+          <t>19929; 41551</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25930; 50233</t>
+          <t>25918; 50715</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27476; 46076</t>
+          <t>28928; 49107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20252; 39871</t>
+          <t>20330; 40919</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24402; 46060</t>
+          <t>24253; 45507</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19753; 41027</t>
+          <t>19766; 41863</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9209; 37569</t>
+          <t>19225; 33779</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39558; 65549</t>
+          <t>40907; 66233</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48988; 80141</t>
+          <t>49656; 80227</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51011; 83281</t>
+          <t>50779; 84118</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28518; 77922</t>
+          <t>51959; 76102</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71808</t>
+          <t>76762</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12310; 29552</t>
+          <t>12019; 29321</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25416; 49815</t>
+          <t>25463; 50805</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14775; 31512</t>
+          <t>14312; 30938</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23611; 39806</t>
+          <t>24791; 43236</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22673; 46064</t>
+          <t>22839; 46490</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31992; 57681</t>
+          <t>33221; 60241</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27725; 54933</t>
+          <t>27086; 55529</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>32440; 49797</t>
+          <t>35131; 53542</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>39215; 67110</t>
+          <t>39586; 68360</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64873; 100318</t>
+          <t>62251; 100315</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47631; 78647</t>
+          <t>47370; 78586</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>60563; 85840</t>
+          <t>65159; 90385</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>114249; 160390</t>
+          <t>113852; 161439</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>179576; 238955</t>
+          <t>182917; 241405</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>138742; 189650</t>
+          <t>140882; 189532</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>147065; 219115</t>
+          <t>179132; 233033</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>221283; 281499</t>
+          <t>217521; 281291</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>305250; 377915</t>
+          <t>304653; 372775</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>242355; 309016</t>
+          <t>243318; 308758</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>175872; 249986</t>
+          <t>218887; 275599</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>347926; 424115</t>
+          <t>345434; 423699</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>498597; 594004</t>
+          <t>501056; 597539</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>396945; 480834</t>
+          <t>395829; 484261</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>346082; 448675</t>
+          <t>411442; 487883</t>
         </is>
       </c>
     </row>
